--- a/Master Calculation Workbook.xlsx
+++ b/Master Calculation Workbook.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.009824+00:00</t>
+          <t>2026-09-04T03:32:25.141732+00:00</t>
         </is>
       </c>
     </row>
@@ -1731,12 +1731,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.012009+00:00</t>
+          <t>2026-09-04T03:32:25.145078+00:00</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.014140+00:00</t>
+          <t>2026-09-04T03:32:25.147536+00:00</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.016506+00:00</t>
+          <t>2026-09-04T03:32:25.151504+00:00</t>
         </is>
       </c>
     </row>
@@ -1812,12 +1812,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.018433+00:00</t>
+          <t>2026-09-04T03:32:25.153957+00:00</t>
         </is>
       </c>
     </row>
@@ -1839,12 +1839,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.020357+00:00</t>
+          <t>2026-09-04T03:32:25.156473+00:00</t>
         </is>
       </c>
     </row>
@@ -1866,12 +1866,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.022407+00:00</t>
+          <t>2026-09-04T03:32:25.158777+00:00</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.024423+00:00</t>
+          <t>2026-09-04T03:32:25.161131+00:00</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.026354+00:00</t>
+          <t>2026-09-04T03:32:25.163447+00:00</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.028242+00:00</t>
+          <t>2026-09-04T03:32:25.166017+00:00</t>
         </is>
       </c>
     </row>
@@ -1974,12 +1974,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.030301+00:00</t>
+          <t>2026-09-04T03:32:25.168186+00:00</t>
         </is>
       </c>
     </row>
@@ -2001,12 +2001,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.032140+00:00</t>
+          <t>2026-09-04T03:32:25.170394+00:00</t>
         </is>
       </c>
     </row>
@@ -2028,12 +2028,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.034047+00:00</t>
+          <t>2026-09-04T03:32:25.172940+00:00</t>
         </is>
       </c>
     </row>
@@ -2055,12 +2055,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.035899+00:00</t>
+          <t>2026-09-04T03:32:25.175229+00:00</t>
         </is>
       </c>
     </row>
@@ -2082,12 +2082,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.037818+00:00</t>
+          <t>2026-09-04T03:32:25.177801+00:00</t>
         </is>
       </c>
     </row>
@@ -2109,12 +2109,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.039940+00:00</t>
+          <t>2026-09-04T03:32:25.180017+00:00</t>
         </is>
       </c>
     </row>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.041815+00:00</t>
+          <t>2026-09-04T03:32:25.182318+00:00</t>
         </is>
       </c>
     </row>
@@ -2163,12 +2163,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.043738+00:00</t>
+          <t>2026-09-04T03:32:25.184702+00:00</t>
         </is>
       </c>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.045633+00:00</t>
+          <t>2026-09-04T03:32:25.186911+00:00</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.047449+00:00</t>
+          <t>2026-09-04T03:32:25.189445+00:00</t>
         </is>
       </c>
     </row>
@@ -2244,12 +2244,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.049290+00:00</t>
+          <t>2026-09-04T03:32:25.191957+00:00</t>
         </is>
       </c>
     </row>
@@ -2271,12 +2271,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.213495+00:00</t>
+          <t>2026-09-04T03:32:25.429455+00:00</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.216087+00:00</t>
+          <t>2026-09-04T03:32:25.434929+00:00</t>
         </is>
       </c>
     </row>
@@ -2325,12 +2325,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.218043+00:00</t>
+          <t>2026-09-04T03:32:25.438998+00:00</t>
         </is>
       </c>
     </row>
@@ -2352,12 +2352,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.219816+00:00</t>
+          <t>2026-09-04T03:32:25.443369+00:00</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.442957+00:00</t>
+          <t>2026-09-04T03:32:25.660593+00:00</t>
         </is>
       </c>
     </row>
@@ -2406,12 +2406,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.445530+00:00</t>
+          <t>2026-09-04T03:32:25.665511+00:00</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.865269+00:00</t>
+          <t>2026-09-04T03:32:26.161486+00:00</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2460,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.286807+00:00</t>
+          <t>2026-09-04T03:32:26.661016+00:00</t>
         </is>
       </c>
     </row>
@@ -2487,12 +2487,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.289185+00:00</t>
+          <t>2026-09-04T03:32:26.664117+00:00</t>
         </is>
       </c>
     </row>
@@ -2514,12 +2514,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.291087+00:00</t>
+          <t>2026-09-04T03:32:26.666690+00:00</t>
         </is>
       </c>
     </row>
@@ -2541,12 +2541,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.293547+00:00</t>
+          <t>2026-09-04T03:32:26.669180+00:00</t>
         </is>
       </c>
     </row>
@@ -2568,12 +2568,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.295587+00:00</t>
+          <t>2026-09-04T03:32:26.671909+00:00</t>
         </is>
       </c>
     </row>
@@ -2595,12 +2595,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.297681+00:00</t>
+          <t>2026-09-04T03:32:26.674372+00:00</t>
         </is>
       </c>
     </row>
@@ -2622,12 +2622,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.299920+00:00</t>
+          <t>2026-09-04T03:32:26.676788+00:00</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2649,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.301831+00:00</t>
+          <t>2026-09-04T03:32:26.679095+00:00</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.303727+00:00</t>
+          <t>2026-09-04T03:32:26.681381+00:00</t>
         </is>
       </c>
     </row>
@@ -2703,12 +2703,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.305528+00:00</t>
+          <t>2026-09-04T03:32:26.683934+00:00</t>
         </is>
       </c>
     </row>
@@ -2730,12 +2730,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.449591+00:00</t>
+          <t>2026-09-04T03:32:26.886997+00:00</t>
         </is>
       </c>
     </row>
@@ -2757,12 +2757,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.451512+00:00</t>
+          <t>2026-09-04T03:32:26.889896+00:00</t>
         </is>
       </c>
     </row>
@@ -2784,12 +2784,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.453462+00:00</t>
+          <t>2026-09-04T03:32:26.892191+00:00</t>
         </is>
       </c>
     </row>
@@ -2811,12 +2811,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.455334+00:00</t>
+          <t>2026-09-04T03:32:26.894469+00:00</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2838,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.457046+00:00</t>
+          <t>2026-09-04T03:32:26.896757+00:00</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.379217+00:00</t>
+          <t>2026-09-04T03:32:32.114624+00:00</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.383352+00:00</t>
+          <t>2026-09-04T03:32:32.117714+00:00</t>
         </is>
       </c>
     </row>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.387075+00:00</t>
+          <t>2026-09-04T03:32:32.122354+00:00</t>
         </is>
       </c>
     </row>
@@ -2946,12 +2946,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.390931+00:00</t>
+          <t>2026-09-04T03:32:32.126424+00:00</t>
         </is>
       </c>
     </row>
@@ -2973,12 +2973,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.394914+00:00</t>
+          <t>2026-09-04T03:32:32.132419+00:00</t>
         </is>
       </c>
     </row>
@@ -3000,12 +3000,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.398965+00:00</t>
+          <t>2026-09-04T03:32:32.134597+00:00</t>
         </is>
       </c>
     </row>
@@ -3027,12 +3027,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.402927+00:00</t>
+          <t>2026-09-04T03:32:32.138276+00:00</t>
         </is>
       </c>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.406940+00:00</t>
+          <t>2026-09-04T03:32:32.144409+00:00</t>
         </is>
       </c>
     </row>
@@ -3081,12 +3081,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.410917+00:00</t>
+          <t>2026-09-04T03:32:32.147001+00:00</t>
         </is>
       </c>
     </row>
@@ -3108,12 +3108,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.417429+00:00</t>
+          <t>2026-09-04T03:32:32.150598+00:00</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.419347+00:00</t>
+          <t>2026-09-04T03:32:32.156406+00:00</t>
         </is>
       </c>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.423001+00:00</t>
+          <t>2026-09-04T03:32:32.158442+00:00</t>
         </is>
       </c>
     </row>
@@ -3189,12 +3189,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.426921+00:00</t>
+          <t>2026-09-04T03:32:32.160790+00:00</t>
         </is>
       </c>
     </row>
@@ -3216,12 +3216,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.431323+00:00</t>
+          <t>2026-09-04T03:32:32.166175+00:00</t>
         </is>
       </c>
     </row>
@@ -3243,12 +3243,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.433080+00:00</t>
+          <t>2026-09-04T03:32:32.172389+00:00</t>
         </is>
       </c>
     </row>
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.851161+00:00</t>
+          <t>2026-09-04T03:32:32.719333+00:00</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3297,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.860712+00:00</t>
+          <t>2026-09-04T03:32:32.732174+00:00</t>
         </is>
       </c>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.864491+00:00</t>
+          <t>2026-09-04T03:32:32.736724+00:00</t>
         </is>
       </c>
     </row>
@@ -3351,12 +3351,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.872311+00:00</t>
+          <t>2026-09-04T03:32:32.745915+00:00</t>
         </is>
       </c>
     </row>
@@ -3378,12 +3378,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.875199+00:00</t>
+          <t>2026-09-04T03:32:32.748634+00:00</t>
         </is>
       </c>
     </row>
@@ -3405,12 +3405,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.885537+00:00</t>
+          <t>2026-09-04T03:32:32.752885+00:00</t>
         </is>
       </c>
     </row>
@@ -3432,12 +3432,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.887386+00:00</t>
+          <t>2026-09-04T03:32:32.754925+00:00</t>
         </is>
       </c>
     </row>
@@ -3459,12 +3459,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.891000+00:00</t>
+          <t>2026-09-04T03:32:32.756977+00:00</t>
         </is>
       </c>
     </row>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:37.150489+00:00</t>
+          <t>2026-09-04T03:32:33.046211+00:00</t>
         </is>
       </c>
     </row>
@@ -3513,12 +3513,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.229559+00:00</t>
+          <t>2026-09-04T03:32:39.857803+00:00</t>
         </is>
       </c>
     </row>
@@ -3540,12 +3540,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.234567+00:00</t>
+          <t>2026-09-04T03:32:39.863591+00:00</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.242394+00:00</t>
+          <t>2026-09-04T03:32:39.875282+00:00</t>
         </is>
       </c>
     </row>
@@ -3594,12 +3594,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.246400+00:00</t>
+          <t>2026-09-04T03:32:39.879954+00:00</t>
         </is>
       </c>
     </row>
@@ -3621,12 +3621,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.248285+00:00</t>
+          <t>2026-09-04T03:32:39.882171+00:00</t>
         </is>
       </c>
     </row>
@@ -3648,12 +3648,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.250354+00:00</t>
+          <t>2026-09-04T03:32:39.884508+00:00</t>
         </is>
       </c>
     </row>
@@ -3675,12 +3675,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.252278+00:00</t>
+          <t>2026-09-04T03:32:39.886628+00:00</t>
         </is>
       </c>
     </row>
@@ -3702,12 +3702,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.254234+00:00</t>
+          <t>2026-09-04T03:32:39.888793+00:00</t>
         </is>
       </c>
     </row>
@@ -3729,12 +3729,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.256146+00:00</t>
+          <t>2026-09-04T03:32:39.891019+00:00</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3756,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.258149+00:00</t>
+          <t>2026-09-04T03:32:39.893266+00:00</t>
         </is>
       </c>
     </row>
@@ -3783,12 +3783,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.372489+00:00</t>
+          <t>2026-09-04T03:32:40.156241+00:00</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.375490+00:00</t>
+          <t>2026-09-04T03:32:40.160669+00:00</t>
         </is>
       </c>
     </row>
@@ -3837,12 +3837,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.379189+00:00</t>
+          <t>2026-09-04T03:32:40.166382+00:00</t>
         </is>
       </c>
     </row>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.385495+00:00</t>
+          <t>2026-09-04T03:32:40.170298+00:00</t>
         </is>
       </c>
     </row>
@@ -3891,12 +3891,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.391628+00:00</t>
+          <t>2026-09-04T03:32:40.178529+00:00</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.450938+00:00</t>
+          <t>2026-09-04T03:32:40.245889+00:00</t>
         </is>
       </c>
     </row>
@@ -3945,12 +3945,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.455821+00:00</t>
+          <t>2026-09-04T03:32:40.249838+00:00</t>
         </is>
       </c>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.459621+00:00</t>
+          <t>2026-09-04T03:32:40.254472+00:00</t>
         </is>
       </c>
     </row>
@@ -3999,12 +3999,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.463060+00:00</t>
+          <t>2026-09-04T03:32:40.258222+00:00</t>
         </is>
       </c>
     </row>
@@ -4026,12 +4026,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.471134+00:00</t>
+          <t>2026-09-04T03:32:40.266516+00:00</t>
         </is>
       </c>
     </row>
@@ -4053,12 +4053,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.475008+00:00</t>
+          <t>2026-09-04T03:32:40.272423+00:00</t>
         </is>
       </c>
     </row>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.469924+00:00</t>
+          <t>2026-09-04T03:32:42.799280+00:00</t>
         </is>
       </c>
     </row>
@@ -4107,12 +4107,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.472287+00:00</t>
+          <t>2026-09-04T03:32:42.802773+00:00</t>
         </is>
       </c>
     </row>
@@ -4134,12 +4134,12 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.475411+00:00</t>
+          <t>2026-09-04T03:32:42.806313+00:00</t>
         </is>
       </c>
     </row>
@@ -4161,12 +4161,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.479174+00:00</t>
+          <t>2026-09-04T03:32:42.810264+00:00</t>
         </is>
       </c>
     </row>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.481253+00:00</t>
+          <t>2026-09-04T03:32:42.814162+00:00</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4215,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.483165+00:00</t>
+          <t>2026-09-04T03:32:42.818410+00:00</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4242,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.934585+00:00</t>
+          <t>2026-09-04T03:32:43.376559+00:00</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:53.456941+00:00</t>
+          <t>2026-09-04T03:32:52.180906+00:00</t>
         </is>
       </c>
     </row>
@@ -4296,12 +4296,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:53.463384+00:00</t>
+          <t>2026-09-04T03:32:52.186846+00:00</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:53.473464+00:00</t>
+          <t>2026-09-04T03:32:52.194283+00:00</t>
         </is>
       </c>
     </row>
@@ -4350,12 +4350,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-08-21T22:04:42.383094+00:00</t>
+          <t>2026-09-04T03:34:02.602185+00:00</t>
         </is>
       </c>
     </row>
@@ -4377,12 +4377,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-08-21T22:04:42.391210+00:00</t>
+          <t>2026-09-04T03:34:02.610787+00:00</t>
         </is>
       </c>
     </row>
@@ -4404,12 +4404,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.007285+00:00</t>
+          <t>2026-09-04T03:32:25.138226+00:00</t>
         </is>
       </c>
     </row>
@@ -4431,12 +4431,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.221619+00:00</t>
+          <t>2026-09-04T03:32:25.447245+00:00</t>
         </is>
       </c>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.223379+00:00</t>
+          <t>2026-09-04T03:32:25.450030+00:00</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.225160+00:00</t>
+          <t>2026-09-04T03:32:25.454755+00:00</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.226916+00:00</t>
+          <t>2026-09-04T03:32:25.457552+00:00</t>
         </is>
       </c>
     </row>
@@ -4539,12 +4539,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.451325+00:00</t>
+          <t>2026-09-04T03:32:25.670514+00:00</t>
         </is>
       </c>
     </row>
@@ -4566,12 +4566,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.455343+00:00</t>
+          <t>2026-09-04T03:32:25.674592+00:00</t>
         </is>
       </c>
     </row>
@@ -4593,12 +4593,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.867824+00:00</t>
+          <t>2026-09-04T03:32:26.164800+00:00</t>
         </is>
       </c>
     </row>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.461084+00:00</t>
+          <t>2026-09-04T03:32:26.901471+00:00</t>
         </is>
       </c>
     </row>
@@ -4647,12 +4647,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:37.152949+00:00</t>
+          <t>2026-09-04T03:32:33.049122+00:00</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4674,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.232092+00:00</t>
+          <t>2026-09-04T03:32:39.861222+00:00</t>
         </is>
       </c>
     </row>
@@ -4701,12 +4701,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.244458+00:00</t>
+          <t>2026-09-04T03:32:39.877746+00:00</t>
         </is>
       </c>
     </row>
@@ -4728,12 +4728,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.388063+00:00</t>
+          <t>2026-09-04T03:32:40.176419+00:00</t>
         </is>
       </c>
     </row>
@@ -4755,12 +4755,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:43.467097+00:00</t>
+          <t>2026-09-04T03:32:40.264423+00:00</t>
         </is>
       </c>
     </row>
@@ -4782,12 +4782,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.487157+00:00</t>
+          <t>2026-09-04T03:32:42.822215+00:00</t>
         </is>
       </c>
     </row>
@@ -4809,12 +4809,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:45.937076+00:00</t>
+          <t>2026-09-04T03:32:43.382775+00:00</t>
         </is>
       </c>
     </row>
@@ -4836,12 +4836,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:53.467052+00:00</t>
+          <t>2026-09-04T03:32:52.189165+00:00</t>
         </is>
       </c>
     </row>
@@ -4863,12 +4863,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>2026-08-21T22:04:42.385962+00:00</t>
+          <t>2026-09-04T03:34:02.605627+00:00</t>
         </is>
       </c>
     </row>
@@ -4890,12 +4890,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>2026-08-21T22:04:42.395034+00:00</t>
+          <t>2026-09-04T03:34:02.614400+00:00</t>
         </is>
       </c>
     </row>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.463498+00:00</t>
+          <t>2026-09-04T03:32:25.684858+00:00</t>
         </is>
       </c>
     </row>
@@ -4944,12 +4944,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:33.465463+00:00</t>
+          <t>2026-09-04T03:32:25.690721+00:00</t>
         </is>
       </c>
     </row>
@@ -4971,12 +4971,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.380446+00:00</t>
+          <t>2026-09-04T03:32:26.803786+00:00</t>
         </is>
       </c>
     </row>
@@ -4998,12 +4998,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.383016+00:00</t>
+          <t>2026-09-04T03:32:26.806889+00:00</t>
         </is>
       </c>
     </row>
@@ -5025,12 +5025,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.385512+00:00</t>
+          <t>2026-09-04T03:32:26.809536+00:00</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.387790+00:00</t>
+          <t>2026-09-04T03:32:26.811823+00:00</t>
         </is>
       </c>
     </row>
@@ -5079,12 +5079,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.389815+00:00</t>
+          <t>2026-09-04T03:32:26.814249+00:00</t>
         </is>
       </c>
     </row>
@@ -5106,12 +5106,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.391836+00:00</t>
+          <t>2026-09-04T03:32:26.816590+00:00</t>
         </is>
       </c>
     </row>
@@ -5133,12 +5133,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.394215+00:00</t>
+          <t>2026-09-04T03:32:26.818759+00:00</t>
         </is>
       </c>
     </row>
@@ -5160,12 +5160,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.396623+00:00</t>
+          <t>2026-09-04T03:32:26.821213+00:00</t>
         </is>
       </c>
     </row>
@@ -5187,12 +5187,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.398549+00:00</t>
+          <t>2026-09-04T03:32:26.823632+00:00</t>
         </is>
       </c>
     </row>
@@ -5214,12 +5214,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.400959+00:00</t>
+          <t>2026-09-04T03:32:26.825829+00:00</t>
         </is>
       </c>
     </row>
@@ -5241,12 +5241,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.403416+00:00</t>
+          <t>2026-09-04T03:32:26.828028+00:00</t>
         </is>
       </c>
     </row>
@@ -5268,12 +5268,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.405346+00:00</t>
+          <t>2026-09-04T03:32:26.830300+00:00</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.407728+00:00</t>
+          <t>2026-09-04T03:32:26.833389+00:00</t>
         </is>
       </c>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.409606+00:00</t>
+          <t>2026-09-04T03:32:26.835779+00:00</t>
         </is>
       </c>
     </row>
@@ -5349,12 +5349,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.411896+00:00</t>
+          <t>2026-09-04T03:32:26.838046+00:00</t>
         </is>
       </c>
     </row>
@@ -5376,12 +5376,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.413881+00:00</t>
+          <t>2026-09-04T03:32:26.840241+00:00</t>
         </is>
       </c>
     </row>
@@ -5403,12 +5403,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.416231+00:00</t>
+          <t>2026-09-04T03:32:26.842461+00:00</t>
         </is>
       </c>
     </row>
@@ -5430,12 +5430,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.418148+00:00</t>
+          <t>2026-09-04T03:32:26.844780+00:00</t>
         </is>
       </c>
     </row>
@@ -5457,12 +5457,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.420467+00:00</t>
+          <t>2026-09-04T03:32:26.847042+00:00</t>
         </is>
       </c>
     </row>
@@ -5484,12 +5484,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.422530+00:00</t>
+          <t>2026-09-04T03:32:26.849335+00:00</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.424351+00:00</t>
+          <t>2026-09-04T03:32:26.851639+00:00</t>
         </is>
       </c>
     </row>
@@ -5538,12 +5538,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.426351+00:00</t>
+          <t>2026-09-04T03:32:26.854100+00:00</t>
         </is>
       </c>
     </row>
@@ -5565,12 +5565,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.428716+00:00</t>
+          <t>2026-09-04T03:32:26.856575+00:00</t>
         </is>
       </c>
     </row>
@@ -5592,12 +5592,12 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.430669+00:00</t>
+          <t>2026-09-04T03:32:26.858807+00:00</t>
         </is>
       </c>
     </row>
@@ -5619,12 +5619,12 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.432504+00:00</t>
+          <t>2026-09-04T03:32:26.861125+00:00</t>
         </is>
       </c>
     </row>
@@ -5646,12 +5646,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.434921+00:00</t>
+          <t>2026-09-04T03:32:26.863289+00:00</t>
         </is>
       </c>
     </row>
@@ -5673,12 +5673,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.436809+00:00</t>
+          <t>2026-09-04T03:32:26.865551+00:00</t>
         </is>
       </c>
     </row>
@@ -5700,12 +5700,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.438629+00:00</t>
+          <t>2026-09-04T03:32:26.868150+00:00</t>
         </is>
       </c>
     </row>
@@ -5727,12 +5727,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.440712+00:00</t>
+          <t>2026-09-04T03:32:26.870727+00:00</t>
         </is>
       </c>
     </row>
@@ -5754,12 +5754,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:34.459389+00:00</t>
+          <t>2026-09-04T03:32:26.899106+00:00</t>
         </is>
       </c>
     </row>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.853553+00:00</t>
+          <t>2026-09-04T03:32:32.722204+00:00</t>
         </is>
       </c>
     </row>
@@ -5808,12 +5808,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.855482+00:00</t>
+          <t>2026-09-04T03:32:32.724547+00:00</t>
         </is>
       </c>
     </row>
@@ -5835,12 +5835,12 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>ed99331a45c4</t>
+          <t>0a27ac7779fa</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>2026-08-21T22:03:36.878970+00:00</t>
+          <t>2026-09-04T03:32:32.750724+00:00</t>
         </is>
       </c>
     </row>
